--- a/04_번역원고_및_임상매트릭스/영추경맥_수태음시동병_매트릭스/영추경맥_수태음시동병_해부임상_매트릭스.xlsx
+++ b/04_번역원고_및_임상매트릭스/영추경맥_수태음시동병_매트릭스/영추경맥_수태음시동병_해부임상_매트릭스.xlsx
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.927</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="6">
@@ -731,7 +731,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"A1_수태음본경_아래팔": ["Cephalic vein", "Radial artery", "Radial vein", "Brachioradialis", "Pronator quadratus", "Flexor digitorum superficialis", "Flexor pollicis longus"], "A2_앞가슴벽": ["External intercostal muscle", "Internal intercostal muscle", "Internal thoracic vein", "Pectoralis minor", "Internal thoracic artery", "Transversus thoracis", "Lateral thoracic artery"], "B2_목앞_빗장위": ["Common carotid artery", "Internal thoracic vein", "Sternohyoid", "Omohyoid", "Sternocleidomastoid", "Platysma"], "B1_등_흉추옆": ["Transverse cervical artery", "Splenius cervicis", "Longissimus", "Rhomboid major"]}</t>
+          <t>{"A1_수태음본경_아래팔": ["Cephalic vein", "Radial artery", "Radial vein", "Brachioradialis", "Pronator quadratus", "Flexor digitorum superficialis", "Set of dorsal digital veins"], "A2_앞가슴벽": ["External intercostal muscle", "Internal intercostal muscle", "Internal thoracic vein", "Internal thoracic artery", "Transversus thoracis", "Pectoralis minor", "Lateral thoracic artery"], "B2_목앞_빗장위": ["Common carotid artery", "Internal thoracic vein", "Sternohyoid", "Omohyoid", "Sternocleidomastoid", "Platysma"], "B1_등_흉추옆": ["Transverse cervical artery", "Splenius cervicis", "Longissimus", "Rhomboid major"]}</t>
         </is>
       </c>
     </row>
@@ -13862,20 +13862,16 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Common fibular nerve; Intermediate dorsal cutaneous nerve; Sacral nerve plexus; Sciatic nerve; Superficial fibular nerve</t>
+          <t>Common fibular nerve; Deep fibular nerve; Fifth common plantar digital nerve; Intermediate dorsal cutaneous nerve; Lateral plantar nerve; Medial terminal branch of deep fibular nerve; Sacral nerve plexus; Sciatic nerve; Superficial branch of lateral plantar nerve; Superficial fibular nerve; Tibial nerve</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>9</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Extensor digitorum longus; Fourth dorsal interosseous of foot</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>L5:B1; S1:B1; L4:B1; S2:B1; S3:B1; S4:B1</t>
+          <t>L5:B1/FMA; S1:B1/FMA; L4:B1; S2:B1/FMA; S3:B1/FMA; S4:B1</t>
         </is>
       </c>
     </row>
@@ -14016,26 +14012,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C6, C7, C8, T1</t>
+          <t>C5, C6, C7, C8, T1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deep branch of ulnar nerve; Peripheral segment of ulnar nerve; Set of dorsal digital branches of radial nerve; Set of proper palmar digital nerves</t>
+          <t>Deep branch of ulnar nerve; Peripheral segment of ulnar nerve; Posterior interosseous nerve; Radial nerve; Set of dorsal digital branches of radial nerve; Set of proper palmar digital nerves</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Extensor indicis</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C6:B1; C7:B1; C8:B1/FMA; T1:B1/FMA</t>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1; C6:B1; T1:B1/FMA</t>
         </is>
       </c>
     </row>
@@ -14137,17 +14129,13 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lateral cutaneous nerve of forearm; Median nerve; Peripheral segment of musculocutaneous nerve; Radial nerve</t>
+          <t>Lateral cutaneous nerve of forearm; Median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of radial nerve; Radial nerve</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>11</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Brachioradialis; Brachialis</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>C5:B1/FMA; C6:B1/FMA; C7:B1; C8:B1; T1:B1</t>
@@ -14178,20 +14166,16 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Radial nerve; Superficial branch of radial nerve</t>
+          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of radial nerve; Posterior interosseous nerve; Radial nerve; Superficial branch of radial nerve</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Abductor pollicis longus; Extensor pollicis brevis; Brachioradialis</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C5:B1; C6:B1; C7:B1/FMA; C8:B1/FMA; T1:B1</t>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1/FMA; C6:B1/FMA; T1:B1</t>
         </is>
       </c>
     </row>
@@ -14219,20 +14203,16 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Radial nerve; Superficial branch of radial nerve</t>
+          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of radial nerve; Posterior interosseous nerve; Radial nerve; Superficial branch of radial nerve</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>17</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Abductor pollicis longus; Extensor pollicis longus; Brachioradialis</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C6:B1/FMA; C7:B1/FMA; C8:B1/FMA; T1:B1/FMA; C5:B1</t>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1/FMA; C6:B1/FMA; T1:B1/FMA</t>
         </is>
       </c>
     </row>
@@ -14291,26 +14271,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C8, T1</t>
+          <t>C5, C6, C7, C8, T1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deep branch of ulnar nerve; Peripheral segment of ulnar nerve; Set of proper palmar digital nerves</t>
+          <t>Deep branch of ulnar nerve; Peripheral segment of ulnar nerve; Posterior interosseous nerve; Radial nerve; Set of proper palmar digital nerves</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>12</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Extensor digiti minimi; Extensor digitorum</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C8:B1/FMA; T1:B1/FMA</t>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1; C6:B1; T1:B1/FMA</t>
         </is>
       </c>
     </row>
@@ -14664,14 +14640,10 @@
       <c r="G27" t="n">
         <v>13</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Flexor hallucis longus; Flexor digitorum longus; Plantaris</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>S1:B1; S2:B1; L4:B1; L5:B1; S3:B1; S4:B1; L3:B1; L2:B1</t>
+          <t>L4:B1; L5:B1/FMA; S1:B1/FMA; S2:B1/FMA; S3:B1; S4:B1; L3:B1; L2:B1</t>
         </is>
       </c>
     </row>
@@ -14693,13 +14665,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C8, T1, T6</t>
+          <t>C8, T1, T6, T8, T9, T10, T11, T12, L1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Medial pectoral nerve; Sixth intercostal nerve</t>
+          <t>Eighth intercostal nerve; Eleventh intercostal nerve; Iliohypogastric nerve; Ilioinguinal nerve; Medial pectoral nerve; Ninth intercostal nerve; Sixth intercostal nerve; Subcostal nerve; Tenth intercostal nerve</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -14707,12 +14679,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>External oblique; Internal oblique; Transversus abdominis</t>
+          <t>External oblique; Transversus abdominis</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>T6:FMA/FMA 라벨; C8:B1; T1:B1</t>
+          <t>T12:B1; L1:B1; T8:FMA 라벨; T9:FMA 라벨; T10:FMA 라벨; T11:FMA 라벨; T6:FMA/FMA 라벨; C8:B1; T1:B1</t>
         </is>
       </c>
     </row>
@@ -14814,20 +14786,16 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of ulnar nerve; Radial nerve; Superficial branch of radial nerve</t>
+          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of radial nerve; Peripheral segment of ulnar nerve; Radial nerve; Superficial branch of radial nerve</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>13</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Brachioradialis</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C6:B1/FMA; C7:B1/FMA; C8:B1/FMA; T1:B1/FMA; C5:B1</t>
+          <t>C5:B1/FMA; C6:B1/FMA; C7:B1/FMA; C8:B1/FMA; T1:B1/FMA</t>
         </is>
       </c>
     </row>
@@ -14855,20 +14823,16 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Radial nerve; Superficial branch of radial nerve</t>
+          <t>Anterior interosseous nerve; Lateral cutaneous nerve of forearm; Peripheral segment of median nerve; Peripheral segment of musculocutaneous nerve; Peripheral segment of radial nerve; Posterior interosseous nerve; Radial nerve; Superficial branch of radial nerve</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>9</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Abductor pollicis longus; Extensor pollicis brevis; Brachioradialis</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C5:B1; C6:B1; C7:B1/FMA; C8:B1/FMA; T1:B1</t>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1/FMA; C6:B1/FMA; T1:B1</t>
         </is>
       </c>
     </row>
@@ -15060,22 +15024,26 @@
           <t>손가락</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C5, C6, C7, C8, T1</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Set of proper palmar digital nerves</t>
+          <t>Posterior interosseous nerve; Radial nerve; Set of proper palmar digital nerves</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>7</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Extensor indicis</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C7:B1/FMA; C8:B1/FMA; C5:B1; C6:B1; T1:B1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15396,7 +15364,7 @@
         <v>0.082</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="L2" t="n">
         <v>0.082</v>
@@ -15417,7 +15385,7 @@
         <v>0.055</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="S2" t="n">
         <v>0.067</v>
@@ -15447,7 +15415,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AC2" t="n">
         <v>0.027</v>
@@ -15474,7 +15442,7 @@
         <v>0.082</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AL2" t="n">
         <v>0.055</v>
@@ -15517,7 +15485,7 @@
         <v>0.225</v>
       </c>
       <c r="K3" t="n">
-        <v>0.112</v>
+        <v>0.15</v>
       </c>
       <c r="L3" t="n">
         <v>0.225</v>
@@ -15538,7 +15506,7 @@
         <v>0.133</v>
       </c>
       <c r="R3" t="n">
-        <v>0.037</v>
+        <v>0.15</v>
       </c>
       <c r="S3" t="n">
         <v>0.14</v>
@@ -15568,7 +15536,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="AC3" t="n">
         <v>0.15</v>
@@ -15595,7 +15563,7 @@
         <v>0.148</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0.133</v>
@@ -15689,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.217</v>
+        <v>0.068</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -15880,7 +15848,7 @@
         <v>0.171</v>
       </c>
       <c r="K6" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="L6" t="n">
         <v>0.132</v>
@@ -15889,10 +15857,10 @@
         <v>0.037</v>
       </c>
       <c r="N6" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="P6" t="n">
         <v>0.039</v>
@@ -15901,7 +15869,7 @@
         <v>0.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05</v>
+        <v>0.033</v>
       </c>
       <c r="S6" t="n">
         <v>0.052</v>
@@ -15931,7 +15899,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="AC6" t="n">
         <v>0.039</v>
@@ -15940,10 +15908,10 @@
         <v>0.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="AG6" t="n">
         <v>0.092</v>
@@ -15958,7 +15926,7 @@
         <v>0.062</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="AL6" t="n">
         <v>0.057</v>
@@ -16013,16 +15981,16 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="P7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -16049,7 +16017,7 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -16064,7 +16032,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -16073,7 +16041,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -16122,7 +16090,7 @@
         <v>0.186</v>
       </c>
       <c r="K8" t="n">
-        <v>0.378</v>
+        <v>0.304</v>
       </c>
       <c r="L8" t="n">
         <v>0.195</v>
@@ -16131,19 +16099,19 @@
         <v>0.395</v>
       </c>
       <c r="N8" t="n">
-        <v>0.296</v>
+        <v>0.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0.356</v>
+        <v>0.339</v>
       </c>
       <c r="P8" t="n">
-        <v>0.371</v>
+        <v>0.354</v>
       </c>
       <c r="Q8" t="n">
         <v>0.222</v>
       </c>
       <c r="R8" t="n">
-        <v>0.269</v>
+        <v>0.339</v>
       </c>
       <c r="S8" t="n">
         <v>0.219</v>
@@ -16173,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.128</v>
+        <v>0.062</v>
       </c>
       <c r="AC8" t="n">
         <v>0.263</v>
@@ -16182,10 +16150,10 @@
         <v>0.265</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.409</v>
+        <v>0.395</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.351</v>
+        <v>0.335</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -16200,7 +16168,7 @@
         <v>0.213</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AL8" t="n">
         <v>0.222</v>
@@ -16243,7 +16211,7 @@
         <v>0.404</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L9" t="n">
         <v>0.271</v>
@@ -16252,19 +16220,19 @@
         <v>0.207</v>
       </c>
       <c r="N9" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="O9" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="P9" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="Q9" t="n">
         <v>0.412</v>
       </c>
       <c r="R9" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="S9" t="n">
         <v>0.444</v>
@@ -16291,10 +16259,10 @@
         <v>0.581</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AC9" t="n">
         <v>0.296</v>
@@ -16303,10 +16271,10 @@
         <v>0.257</v>
       </c>
       <c r="AE9" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.257</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.258</v>
       </c>
       <c r="AG9" t="n">
         <v>0.047</v>
@@ -16321,7 +16289,7 @@
         <v>0.581</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="AL9" t="n">
         <v>0.496</v>
@@ -16364,7 +16332,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.171</v>
+        <v>0.214</v>
       </c>
       <c r="L10" t="n">
         <v>0.382</v>
@@ -16373,10 +16341,10 @@
         <v>0.18</v>
       </c>
       <c r="N10" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="O10" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="P10" t="n">
         <v>0.221</v>
@@ -16385,7 +16353,7 @@
         <v>0.353</v>
       </c>
       <c r="R10" t="n">
-        <v>0.093</v>
+        <v>0.221</v>
       </c>
       <c r="S10" t="n">
         <v>0.376</v>
@@ -16412,10 +16380,10 @@
         <v>0.404</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.166</v>
+        <v>0.112</v>
       </c>
       <c r="AC10" t="n">
         <v>0.258</v>
@@ -16424,10 +16392,10 @@
         <v>0.222</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.223</v>
+        <v>0.221</v>
       </c>
       <c r="AG10" t="n">
         <v>0.112</v>
@@ -16442,7 +16410,7 @@
         <v>0.404</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.223</v>
       </c>
       <c r="AL10" t="n">
         <v>0.415</v>
@@ -16458,10 +16426,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="C11" t="n">
-        <v>0.112</v>
+        <v>0.15</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -16470,106 +16438,106 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.378</v>
+        <v>0.304</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.171</v>
+        <v>0.214</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.171</v>
+        <v>0.214</v>
       </c>
       <c r="M11" t="n">
-        <v>0.572</v>
+        <v>0.463</v>
       </c>
       <c r="N11" t="n">
-        <v>0.249</v>
+        <v>0.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0.24</v>
+        <v>0.373</v>
       </c>
       <c r="P11" t="n">
-        <v>0.24</v>
+        <v>0.372</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0.461</v>
+        <v>0.643</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="W11" t="n">
-        <v>0.129</v>
+        <v>0.171</v>
       </c>
       <c r="X11" t="n">
-        <v>0.339</v>
+        <v>0.272</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.275</v>
+        <v>0.365</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.24</v>
+        <v>0.374</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.043</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.19</v>
+        <v>0.594</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -16606,7 +16574,7 @@
         <v>0.382</v>
       </c>
       <c r="K12" t="n">
-        <v>0.171</v>
+        <v>0.214</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -16615,19 +16583,19 @@
         <v>0.171</v>
       </c>
       <c r="N12" t="n">
-        <v>0.281</v>
+        <v>0.276</v>
       </c>
       <c r="O12" t="n">
-        <v>0.261</v>
+        <v>0.257</v>
       </c>
       <c r="P12" t="n">
-        <v>0.267</v>
+        <v>0.262</v>
       </c>
       <c r="Q12" t="n">
         <v>0.303</v>
       </c>
       <c r="R12" t="n">
-        <v>0.091</v>
+        <v>0.219</v>
       </c>
       <c r="S12" t="n">
         <v>0.341</v>
@@ -16657,7 +16625,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.125</v>
+        <v>0.082</v>
       </c>
       <c r="AC12" t="n">
         <v>0.334</v>
@@ -16666,10 +16634,10 @@
         <v>0.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.249</v>
+        <v>0.245</v>
       </c>
       <c r="AG12" t="n">
         <v>0.112</v>
@@ -16684,7 +16652,7 @@
         <v>0.271</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AL12" t="n">
         <v>0.317</v>
@@ -16727,7 +16695,7 @@
         <v>0.18</v>
       </c>
       <c r="K13" t="n">
-        <v>0.572</v>
+        <v>0.463</v>
       </c>
       <c r="L13" t="n">
         <v>0.171</v>
@@ -16736,19 +16704,19 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.284</v>
+        <v>0.28</v>
       </c>
       <c r="O13" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="P13" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="Q13" t="n">
         <v>0.208</v>
       </c>
       <c r="R13" t="n">
-        <v>0.401</v>
+        <v>0.451</v>
       </c>
       <c r="S13" t="n">
         <v>0.207</v>
@@ -16775,10 +16743,10 @@
         <v>0.207</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.12</v>
+        <v>0.055</v>
       </c>
       <c r="AC13" t="n">
         <v>0.261</v>
@@ -16787,10 +16755,10 @@
         <v>0.267</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -16805,7 +16773,7 @@
         <v>0.207</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.253</v>
+        <v>0.46</v>
       </c>
       <c r="AL13" t="n">
         <v>0.208</v>
@@ -16833,106 +16801,106 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.296</v>
+        <v>0.29</v>
       </c>
       <c r="I14" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="J14" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="K14" t="n">
-        <v>0.249</v>
+        <v>0.35</v>
       </c>
       <c r="L14" t="n">
-        <v>0.281</v>
+        <v>0.276</v>
       </c>
       <c r="M14" t="n">
-        <v>0.284</v>
+        <v>0.28</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.55</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.54</v>
+        <v>0.554</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="R14" t="n">
-        <v>0.136</v>
+        <v>0.367</v>
       </c>
       <c r="S14" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="T14" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="U14" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="V14" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="W14" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="X14" t="n">
-        <v>0.294</v>
+        <v>0.287</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.532</v>
+        <v>0.569</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.534</v>
+        <v>0.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.543</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AG14" t="n">
         <v>0.037</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="AI14" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01</v>
+        <v>0.367</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.268</v>
+        <v>0.266</v>
       </c>
     </row>
     <row r="15">
@@ -16954,46 +16922,46 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="G15" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H15" t="n">
-        <v>0.356</v>
+        <v>0.339</v>
       </c>
       <c r="I15" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.257</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.261</v>
-      </c>
       <c r="M15" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="N15" t="n">
-        <v>0.55</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.858</v>
+        <v>0.865</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.266</v>
+        <v>0.264</v>
       </c>
       <c r="R15" t="n">
-        <v>0.136</v>
+        <v>0.391</v>
       </c>
       <c r="S15" t="n">
-        <v>0.263</v>
+        <v>0.262</v>
       </c>
       <c r="T15" t="n">
         <v>0.167</v>
@@ -17005,34 +16973,34 @@
         <v>0.037</v>
       </c>
       <c r="W15" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="X15" t="n">
-        <v>0.35</v>
+        <v>0.332</v>
       </c>
       <c r="Y15" t="n">
         <v>0.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.388</v>
+        <v>0.404</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.41</v>
+        <v>0.429</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.751</v>
+        <v>0.727</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.877</v>
+        <v>0.884</v>
       </c>
       <c r="AG15" t="n">
         <v>0.037</v>
@@ -17041,19 +17009,19 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AM15" t="n">
         <v>0.257</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.258</v>
       </c>
     </row>
     <row r="16">
@@ -17078,43 +17046,43 @@
         <v>0.039</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H16" t="n">
-        <v>0.371</v>
+        <v>0.354</v>
       </c>
       <c r="I16" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="J16" t="n">
         <v>0.221</v>
       </c>
       <c r="K16" t="n">
-        <v>0.24</v>
+        <v>0.372</v>
       </c>
       <c r="L16" t="n">
-        <v>0.267</v>
+        <v>0.262</v>
       </c>
       <c r="M16" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="N16" t="n">
-        <v>0.54</v>
+        <v>0.554</v>
       </c>
       <c r="O16" t="n">
-        <v>0.858</v>
+        <v>0.865</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.265</v>
+        <v>0.263</v>
       </c>
       <c r="R16" t="n">
-        <v>0.135</v>
+        <v>0.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="T16" t="n">
         <v>0.167</v>
@@ -17126,34 +17094,34 @@
         <v>0.037</v>
       </c>
       <c r="W16" t="n">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="X16" t="n">
-        <v>0.368</v>
+        <v>0.348</v>
       </c>
       <c r="Y16" t="n">
         <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.385</v>
+        <v>0.401</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.406</v>
+        <v>0.426</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.828</v>
+        <v>0.798</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.848</v>
+        <v>0.857</v>
       </c>
       <c r="AG16" t="n">
         <v>0.037</v>
@@ -17162,19 +17130,19 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AM16" t="n">
         <v>0.257</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.258</v>
       </c>
     </row>
     <row r="17">
@@ -17211,7 +17179,7 @@
         <v>0.353</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L17" t="n">
         <v>0.303</v>
@@ -17220,19 +17188,19 @@
         <v>0.208</v>
       </c>
       <c r="N17" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="O17" t="n">
-        <v>0.266</v>
+        <v>0.264</v>
       </c>
       <c r="P17" t="n">
-        <v>0.265</v>
+        <v>0.263</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.115</v>
+        <v>0.264</v>
       </c>
       <c r="S17" t="n">
         <v>0.73</v>
@@ -17259,10 +17227,10 @@
         <v>0.591</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.226</v>
+        <v>0.143</v>
       </c>
       <c r="AC17" t="n">
         <v>0.307</v>
@@ -17271,10 +17239,10 @@
         <v>0.267</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.266</v>
+        <v>0.264</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AG17" t="n">
         <v>0.075</v>
@@ -17289,7 +17257,7 @@
         <v>0.412</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.258</v>
       </c>
       <c r="AL17" t="n">
         <v>0.495</v>
@@ -17305,10 +17273,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="C18" t="n">
-        <v>0.037</v>
+        <v>0.15</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -17317,106 +17285,106 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05</v>
+        <v>0.033</v>
       </c>
       <c r="G18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.269</v>
+        <v>0.339</v>
       </c>
       <c r="I18" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="J18" t="n">
-        <v>0.093</v>
+        <v>0.221</v>
       </c>
       <c r="K18" t="n">
-        <v>0.461</v>
+        <v>0.643</v>
       </c>
       <c r="L18" t="n">
-        <v>0.091</v>
+        <v>0.219</v>
       </c>
       <c r="M18" t="n">
-        <v>0.401</v>
+        <v>0.451</v>
       </c>
       <c r="N18" t="n">
-        <v>0.136</v>
+        <v>0.367</v>
       </c>
       <c r="O18" t="n">
-        <v>0.136</v>
+        <v>0.391</v>
       </c>
       <c r="P18" t="n">
-        <v>0.135</v>
+        <v>0.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.115</v>
+        <v>0.264</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.112</v>
+        <v>0.262</v>
       </c>
       <c r="T18" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="W18" t="n">
-        <v>0.049</v>
+        <v>0.177</v>
       </c>
       <c r="X18" t="n">
-        <v>0.194</v>
+        <v>0.275</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.209</v>
+        <v>0.057</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.127</v>
+        <v>0.307</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.128</v>
+        <v>0.307</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.166</v>
+        <v>0.384</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.128</v>
+        <v>0.385</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.217</v>
+        <v>0.607</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.115</v>
+        <v>0.264</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.117</v>
+        <v>0.265</v>
       </c>
     </row>
     <row r="19">
@@ -17453,7 +17421,7 @@
         <v>0.376</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L19" t="n">
         <v>0.341</v>
@@ -17462,19 +17430,19 @@
         <v>0.207</v>
       </c>
       <c r="N19" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="O19" t="n">
-        <v>0.263</v>
+        <v>0.262</v>
       </c>
       <c r="P19" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="Q19" t="n">
         <v>0.73</v>
       </c>
       <c r="R19" t="n">
-        <v>0.112</v>
+        <v>0.262</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -17501,10 +17469,10 @@
         <v>0.615</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.208</v>
+        <v>0.135</v>
       </c>
       <c r="AC19" t="n">
         <v>0.299</v>
@@ -17513,10 +17481,10 @@
         <v>0.264</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AG19" t="n">
         <v>0.094</v>
@@ -17531,7 +17499,7 @@
         <v>0.444</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.007</v>
+        <v>0.257</v>
       </c>
       <c r="AL19" t="n">
         <v>0.51</v>
@@ -17574,7 +17542,7 @@
         <v>0.349</v>
       </c>
       <c r="K20" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="L20" t="n">
         <v>0.27</v>
@@ -17583,7 +17551,7 @@
         <v>0.133</v>
       </c>
       <c r="N20" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="O20" t="n">
         <v>0.167</v>
@@ -17595,7 +17563,7 @@
         <v>0.158</v>
       </c>
       <c r="R20" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="S20" t="n">
         <v>0.164</v>
@@ -17625,7 +17593,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="AC20" t="n">
         <v>0.175</v>
@@ -17652,7 +17620,7 @@
         <v>0.165</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AL20" t="n">
         <v>0.167</v>
@@ -17704,7 +17672,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -17816,7 +17784,7 @@
         <v>0.197</v>
       </c>
       <c r="K22" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="L22" t="n">
         <v>0.144</v>
@@ -17825,7 +17793,7 @@
         <v>0.043</v>
       </c>
       <c r="N22" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="O22" t="n">
         <v>0.037</v>
@@ -17837,7 +17805,7 @@
         <v>0.051</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="S22" t="n">
         <v>0.055</v>
@@ -17867,7 +17835,7 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="AC22" t="n">
         <v>0.046</v>
@@ -17894,7 +17862,7 @@
         <v>0.068</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AL22" t="n">
         <v>0.062</v>
@@ -17937,7 +17905,7 @@
         <v>0.17</v>
       </c>
       <c r="K23" t="n">
-        <v>0.129</v>
+        <v>0.171</v>
       </c>
       <c r="L23" t="n">
         <v>0.186</v>
@@ -17946,19 +17914,19 @@
         <v>0.129</v>
       </c>
       <c r="N23" t="n">
-        <v>0.194</v>
+        <v>0.192</v>
       </c>
       <c r="O23" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="P23" t="n">
-        <v>0.185</v>
+        <v>0.183</v>
       </c>
       <c r="Q23" t="n">
         <v>0.408</v>
       </c>
       <c r="R23" t="n">
-        <v>0.049</v>
+        <v>0.177</v>
       </c>
       <c r="S23" t="n">
         <v>0.508</v>
@@ -17988,7 +17956,7 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.104</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AC23" t="n">
         <v>0.185</v>
@@ -17997,10 +17965,10 @@
         <v>0.186</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AG23" t="n">
         <v>0.104</v>
@@ -18015,7 +17983,7 @@
         <v>0.201</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AL23" t="n">
         <v>0.224</v>
@@ -18058,7 +18026,7 @@
         <v>0.188</v>
       </c>
       <c r="K24" t="n">
-        <v>0.339</v>
+        <v>0.272</v>
       </c>
       <c r="L24" t="n">
         <v>0.191</v>
@@ -18067,19 +18035,19 @@
         <v>0.364</v>
       </c>
       <c r="N24" t="n">
-        <v>0.294</v>
+        <v>0.287</v>
       </c>
       <c r="O24" t="n">
-        <v>0.35</v>
+        <v>0.332</v>
       </c>
       <c r="P24" t="n">
-        <v>0.368</v>
+        <v>0.348</v>
       </c>
       <c r="Q24" t="n">
         <v>0.217</v>
       </c>
       <c r="R24" t="n">
-        <v>0.194</v>
+        <v>0.275</v>
       </c>
       <c r="S24" t="n">
         <v>0.214</v>
@@ -18109,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.12</v>
+        <v>0.055</v>
       </c>
       <c r="AC24" t="n">
         <v>0.257</v>
@@ -18118,10 +18086,10 @@
         <v>0.259</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.419</v>
+        <v>0.402</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.356</v>
+        <v>0.336</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -18136,7 +18104,7 @@
         <v>0.215</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="AL24" t="n">
         <v>0.217</v>
@@ -18179,7 +18147,7 @@
         <v>0.367</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L25" t="n">
         <v>0.265</v>
@@ -18188,7 +18156,7 @@
         <v>0.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="O25" t="n">
         <v>0.25</v>
@@ -18200,7 +18168,7 @@
         <v>0.384</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="S25" t="n">
         <v>0.405</v>
@@ -18230,7 +18198,7 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AC25" t="n">
         <v>0.296</v>
@@ -18257,7 +18225,7 @@
         <v>0.514</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL25" t="n">
         <v>0.459</v>
@@ -18300,7 +18268,7 @@
         <v>0.404</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L26" t="n">
         <v>0.271</v>
@@ -18309,19 +18277,19 @@
         <v>0.207</v>
       </c>
       <c r="N26" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="O26" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="P26" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="Q26" t="n">
         <v>0.591</v>
       </c>
       <c r="R26" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="S26" t="n">
         <v>0.615</v>
@@ -18348,10 +18316,10 @@
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AC26" t="n">
         <v>0.296</v>
@@ -18360,10 +18328,10 @@
         <v>0.257</v>
       </c>
       <c r="AE26" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AF26" t="n">
         <v>0.257</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.258</v>
       </c>
       <c r="AG26" t="n">
         <v>0.105</v>
@@ -18378,7 +18346,7 @@
         <v>0.581</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="AL26" t="n">
         <v>0.496</v>
@@ -18409,43 +18377,43 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="J27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="K27" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="P27" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="R27" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="S27" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -18466,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -18484,7 +18452,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -18493,19 +18461,19 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="AJ27" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="AM27" t="n">
         <v>0.007</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0.008</v>
       </c>
     </row>
     <row r="28">
@@ -18515,79 +18483,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="C28" t="n">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="D28" t="n">
-        <v>0.217</v>
+        <v>0.068</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.128</v>
+        <v>0.062</v>
       </c>
       <c r="I28" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="J28" t="n">
-        <v>0.166</v>
+        <v>0.112</v>
       </c>
       <c r="K28" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="L28" t="n">
-        <v>0.125</v>
+        <v>0.082</v>
       </c>
       <c r="M28" t="n">
-        <v>0.12</v>
+        <v>0.055</v>
       </c>
       <c r="N28" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="O28" t="n">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="P28" t="n">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.226</v>
+        <v>0.143</v>
       </c>
       <c r="R28" t="n">
-        <v>0.209</v>
+        <v>0.057</v>
       </c>
       <c r="S28" t="n">
-        <v>0.208</v>
+        <v>0.135</v>
       </c>
       <c r="T28" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="W28" t="n">
-        <v>0.104</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="X28" t="n">
-        <v>0.12</v>
+        <v>0.055</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -18596,37 +18564,37 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.157</v>
+        <v>0.096</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.11</v>
+        <v>0.059</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.075</v>
+        <v>0.03</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.246</v>
+        <v>0.148</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.282</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="29">
@@ -18663,7 +18631,7 @@
         <v>0.258</v>
       </c>
       <c r="K29" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="L29" t="n">
         <v>0.334</v>
@@ -18672,19 +18640,19 @@
         <v>0.261</v>
       </c>
       <c r="N29" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0.388</v>
+        <v>0.404</v>
       </c>
       <c r="P29" t="n">
-        <v>0.385</v>
+        <v>0.401</v>
       </c>
       <c r="Q29" t="n">
         <v>0.307</v>
       </c>
       <c r="R29" t="n">
-        <v>0.127</v>
+        <v>0.307</v>
       </c>
       <c r="S29" t="n">
         <v>0.299</v>
@@ -18714,7 +18682,7 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.157</v>
+        <v>0.096</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
@@ -18723,10 +18691,10 @@
         <v>0.8120000000000001</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.386</v>
+        <v>0.406</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.374</v>
+        <v>0.391</v>
       </c>
       <c r="AG29" t="n">
         <v>0.037</v>
@@ -18741,7 +18709,7 @@
         <v>0.296</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AL29" t="n">
         <v>0.309</v>
@@ -18784,7 +18752,7 @@
         <v>0.222</v>
       </c>
       <c r="K30" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="L30" t="n">
         <v>0.31</v>
@@ -18793,19 +18761,19 @@
         <v>0.267</v>
       </c>
       <c r="N30" t="n">
-        <v>0.532</v>
+        <v>0.569</v>
       </c>
       <c r="O30" t="n">
-        <v>0.41</v>
+        <v>0.429</v>
       </c>
       <c r="P30" t="n">
-        <v>0.406</v>
+        <v>0.426</v>
       </c>
       <c r="Q30" t="n">
         <v>0.267</v>
       </c>
       <c r="R30" t="n">
-        <v>0.128</v>
+        <v>0.307</v>
       </c>
       <c r="S30" t="n">
         <v>0.264</v>
@@ -18835,7 +18803,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.11</v>
+        <v>0.059</v>
       </c>
       <c r="AC30" t="n">
         <v>0.8120000000000001</v>
@@ -18844,10 +18812,10 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.406</v>
+        <v>0.432</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="AG30" t="n">
         <v>0.037</v>
@@ -18862,7 +18830,7 @@
         <v>0.257</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AL30" t="n">
         <v>0.267</v>
@@ -18890,46 +18858,46 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.409</v>
+        <v>0.395</v>
       </c>
       <c r="I31" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="J31" t="n">
-        <v>0.222</v>
+        <v>0.221</v>
       </c>
       <c r="K31" t="n">
-        <v>0.275</v>
+        <v>0.365</v>
       </c>
       <c r="L31" t="n">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="M31" t="n">
-        <v>0.298</v>
+        <v>0.294</v>
       </c>
       <c r="N31" t="n">
-        <v>0.534</v>
+        <v>0.57</v>
       </c>
       <c r="O31" t="n">
-        <v>0.751</v>
+        <v>0.727</v>
       </c>
       <c r="P31" t="n">
-        <v>0.828</v>
+        <v>0.798</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.266</v>
+        <v>0.264</v>
       </c>
       <c r="R31" t="n">
-        <v>0.166</v>
+        <v>0.384</v>
       </c>
       <c r="S31" t="n">
-        <v>0.27</v>
+        <v>0.269</v>
       </c>
       <c r="T31" t="n">
         <v>0.167</v>
@@ -18941,34 +18909,34 @@
         <v>0.037</v>
       </c>
       <c r="W31" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="X31" t="n">
-        <v>0.419</v>
+        <v>0.402</v>
       </c>
       <c r="Y31" t="n">
         <v>0.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.386</v>
+        <v>0.406</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.406</v>
+        <v>0.432</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.734</v>
+        <v>0.711</v>
       </c>
       <c r="AG31" t="n">
         <v>0.037</v>
@@ -18980,13 +18948,13 @@
         <v>0.05</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="AM31" t="n">
         <v>0.258</v>
@@ -19011,46 +18979,46 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="G32" t="n">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="H32" t="n">
-        <v>0.351</v>
+        <v>0.335</v>
       </c>
       <c r="I32" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="J32" t="n">
-        <v>0.223</v>
+        <v>0.221</v>
       </c>
       <c r="K32" t="n">
-        <v>0.24</v>
+        <v>0.374</v>
       </c>
       <c r="L32" t="n">
-        <v>0.249</v>
+        <v>0.245</v>
       </c>
       <c r="M32" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="N32" t="n">
-        <v>0.543</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>0.877</v>
+        <v>0.884</v>
       </c>
       <c r="P32" t="n">
-        <v>0.848</v>
+        <v>0.857</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="R32" t="n">
-        <v>0.128</v>
+        <v>0.385</v>
       </c>
       <c r="S32" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="T32" t="n">
         <v>0.167</v>
@@ -19062,31 +19030,31 @@
         <v>0.037</v>
       </c>
       <c r="W32" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="X32" t="n">
-        <v>0.356</v>
+        <v>0.336</v>
       </c>
       <c r="Y32" t="n">
         <v>0.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.374</v>
+        <v>0.391</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.395</v>
+        <v>0.415</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.734</v>
+        <v>0.711</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
@@ -19098,16 +19066,16 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AM32" t="n">
         <v>0.25</v>
@@ -19147,7 +19115,7 @@
         <v>0.112</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="L33" t="n">
         <v>0.112</v>
@@ -19168,7 +19136,7 @@
         <v>0.075</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="S33" t="n">
         <v>0.094</v>
@@ -19198,7 +19166,7 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="AC33" t="n">
         <v>0.037</v>
@@ -19225,7 +19193,7 @@
         <v>0.047</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AL33" t="n">
         <v>0.033</v>
@@ -19268,7 +19236,7 @@
         <v>0.212</v>
       </c>
       <c r="K34" t="n">
-        <v>0.043</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L34" t="n">
         <v>0.177</v>
@@ -19277,7 +19245,7 @@
         <v>0.043</v>
       </c>
       <c r="N34" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="O34" t="n">
         <v>0.08599999999999999</v>
@@ -19289,7 +19257,7 @@
         <v>0.083</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>0.089</v>
@@ -19346,7 +19314,7 @@
         <v>0.082</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AL34" t="n">
         <v>0.083</v>
@@ -19377,7 +19345,7 @@
         <v>0.05</v>
       </c>
       <c r="G35" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H35" t="n">
         <v>0.06</v>
@@ -19389,7 +19357,7 @@
         <v>0.037</v>
       </c>
       <c r="K35" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L35" t="n">
         <v>0.037</v>
@@ -19401,16 +19369,16 @@
         <v>0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="P35" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="Q35" t="n">
         <v>0.043</v>
       </c>
       <c r="R35" t="n">
-        <v>0.109</v>
+        <v>0.058</v>
       </c>
       <c r="S35" t="n">
         <v>0.043</v>
@@ -19437,10 +19405,10 @@
         <v>0.043</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.075</v>
+        <v>0.03</v>
       </c>
       <c r="AC35" t="n">
         <v>0.05</v>
@@ -19452,7 +19420,7 @@
         <v>0.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AG35" t="n">
         <v>0.011</v>
@@ -19467,7 +19435,7 @@
         <v>0.043</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AL35" t="n">
         <v>0.043</v>
@@ -19510,7 +19478,7 @@
         <v>0.404</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L36" t="n">
         <v>0.271</v>
@@ -19519,19 +19487,19 @@
         <v>0.207</v>
       </c>
       <c r="N36" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="O36" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="P36" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="Q36" t="n">
         <v>0.412</v>
       </c>
       <c r="R36" t="n">
-        <v>0.107</v>
+        <v>0.256</v>
       </c>
       <c r="S36" t="n">
         <v>0.444</v>
@@ -19558,10 +19526,10 @@
         <v>0.581</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.233</v>
+        <v>0.149</v>
       </c>
       <c r="AC36" t="n">
         <v>0.296</v>
@@ -19570,10 +19538,10 @@
         <v>0.257</v>
       </c>
       <c r="AE36" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="AF36" t="n">
         <v>0.257</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.258</v>
       </c>
       <c r="AG36" t="n">
         <v>0.047</v>
@@ -19588,7 +19556,7 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="AL36" t="n">
         <v>0.717</v>
@@ -19604,10 +19572,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -19616,106 +19584,106 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="J37" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.223</v>
       </c>
       <c r="K37" t="n">
-        <v>0.19</v>
+        <v>0.594</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="M37" t="n">
-        <v>0.253</v>
+        <v>0.46</v>
       </c>
       <c r="N37" t="n">
-        <v>0.01</v>
+        <v>0.367</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.258</v>
       </c>
       <c r="R37" t="n">
-        <v>0.217</v>
+        <v>0.607</v>
       </c>
       <c r="S37" t="n">
-        <v>0.007</v>
+        <v>0.257</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.008</v>
+        <v>0.258</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.258</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.011</v>
+        <v>0.259</v>
       </c>
     </row>
     <row r="38">
@@ -19752,7 +19720,7 @@
         <v>0.415</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L38" t="n">
         <v>0.317</v>
@@ -19761,19 +19729,19 @@
         <v>0.208</v>
       </c>
       <c r="N38" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="O38" t="n">
-        <v>0.266</v>
+        <v>0.264</v>
       </c>
       <c r="P38" t="n">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="Q38" t="n">
         <v>0.495</v>
       </c>
       <c r="R38" t="n">
-        <v>0.115</v>
+        <v>0.264</v>
       </c>
       <c r="S38" t="n">
         <v>0.51</v>
@@ -19800,10 +19768,10 @@
         <v>0.496</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.246</v>
+        <v>0.148</v>
       </c>
       <c r="AC38" t="n">
         <v>0.309</v>
@@ -19812,10 +19780,10 @@
         <v>0.267</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.275</v>
+        <v>0.273</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AG38" t="n">
         <v>0.033</v>
@@ -19830,7 +19798,7 @@
         <v>0.717</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.258</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
@@ -19873,7 +19841,7 @@
         <v>0.413</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L39" t="n">
         <v>0.288</v>
@@ -19882,19 +19850,19 @@
         <v>0.209</v>
       </c>
       <c r="N39" t="n">
-        <v>0.268</v>
+        <v>0.266</v>
       </c>
       <c r="O39" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="P39" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="Q39" t="n">
         <v>0.478</v>
       </c>
       <c r="R39" t="n">
-        <v>0.117</v>
+        <v>0.265</v>
       </c>
       <c r="S39" t="n">
         <v>0.471</v>
@@ -19921,10 +19889,10 @@
         <v>0.494</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.282</v>
+        <v>0.183</v>
       </c>
       <c r="AC39" t="n">
         <v>0.312</v>
@@ -19951,7 +19919,7 @@
         <v>0.494</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.011</v>
+        <v>0.259</v>
       </c>
       <c r="AL39" t="n">
         <v>0.606</v>
@@ -20032,7 +20000,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20062,7 +20030,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20092,7 +20060,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -20101,7 +20069,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -20131,7 +20099,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -20152,7 +20120,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -20221,7 +20189,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -20251,7 +20219,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -20307,11 +20275,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A3 손가락</t>
+          <t>A1 수태음 본경·손목 자쪽</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -20337,7 +20305,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -20367,11 +20335,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A3 손가락</t>
+          <t>A1 수태음 본경·손목 자쪽</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -20401,7 +20369,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -20431,7 +20399,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -20461,7 +20429,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -20491,7 +20459,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -20517,11 +20485,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A3 손가락</t>
+          <t>A1 수태음 본경·손목 자쪽</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -20551,7 +20519,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -20572,7 +20540,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -20602,7 +20570,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20632,7 +20600,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20667,7 +20635,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -20701,7 +20669,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -20731,7 +20699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -20761,7 +20729,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -20821,7 +20789,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -20851,7 +20819,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -20881,7 +20849,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -20911,7 +20879,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -20941,7 +20909,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -20962,7 +20930,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -20992,7 +20960,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B 목·등 분절축</t>
+          <t>A 팔신경얼기 영역</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -21031,7 +20999,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -21061,7 +21029,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -21087,11 +21055,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>A6 집게손가락 끝(商陽)</t>
+          <t>A1 수태음 본경·손목 자쪽</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -21121,7 +21089,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -21151,7 +21119,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -21271,7 +21239,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>0.235</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21287,7 +21255,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LU7(0.86); LU8(0.85); LU6(0.83)</t>
+          <t>LU7(0.87); LU8(0.86); LU6(0.80)</t>
         </is>
       </c>
     </row>
@@ -21314,17 +21282,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>0.819</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21340,7 +21308,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LU8(0.88); LU9(0.86); LU6(0.75)</t>
+          <t>LU8(0.88); LU9(0.87); LU6(0.73)</t>
         </is>
       </c>
     </row>
@@ -21367,17 +21335,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.793</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.233</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21393,7 +21361,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LU7(0.88); LU9(0.85); LU6(0.73)</t>
+          <t>LU7(0.88); LU9(0.86); LU6(0.71)</t>
         </is>
       </c>
     </row>
@@ -21420,17 +21388,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.773</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21446,7 +21414,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LU9(0.83); LU7(0.75); LU8(0.73)</t>
+          <t>LU9(0.80); LU7(0.73); LU8(0.71)</t>
         </is>
       </c>
     </row>
@@ -21473,17 +21441,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.508</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21499,7 +21467,7 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LU7(0.55); LU8(0.54); LU9(0.54)</t>
+          <t>LU6(0.57); LU4(0.57); LU7(0.56)</t>
         </is>
       </c>
     </row>
@@ -21526,17 +21494,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.426</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21552,7 +21520,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LU3(0.81); LU5(0.53); LU7(0.41)</t>
+          <t>LU3(0.81); LU5(0.57); LU6(0.43)</t>
         </is>
       </c>
     </row>
@@ -21579,17 +21547,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>0.401</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21605,7 +21573,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LU4(0.81); LU5(0.48); LU7(0.39)</t>
+          <t>LU4(0.81); LU5(0.50); LU6(0.41)</t>
         </is>
       </c>
     </row>
@@ -21617,48 +21585,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HT7</t>
+          <t>LI1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>神門</t>
+          <t>商陽</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>3층</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>손목 자쪽</t>
+          <t>손가락</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C6,C7,C8,T1</t>
+          <t>C5,C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>HT6(0.86); LU6(0.41); LU11(0.40)</t>
+          <t>SI2(0.61); LI3(0.59); LU11(0.46)</t>
         </is>
       </c>
     </row>
@@ -21670,48 +21638,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HT6</t>
+          <t>SI2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陰郄</t>
+          <t>前谷</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>손목 자쪽</t>
+          <t>손가락</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C6,C7,C8,T1</t>
+          <t>C5,C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>HT7(0.86); LU6(0.42); LU9(0.37)</t>
+          <t>LI3(0.64); LI1(0.61); LU11(0.45)</t>
         </is>
       </c>
     </row>
@@ -21723,48 +21691,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ST16</t>
+          <t>LI3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>膺窗</t>
+          <t>三間</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.314</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.205</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>흉벽 앞</t>
+          <t>손</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T3</t>
+          <t>C5,C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>KI24(0.72); ST18(0.61); SP18(0.51)</t>
+          <t>SI2(0.64); LI1(0.59); LU11(0.46)</t>
         </is>
       </c>
     </row>
@@ -21776,12 +21744,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SP18</t>
+          <t>HT7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>天谿</t>
+          <t>神門</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21791,33 +21759,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>흉벽 전외측</t>
+          <t>손목 자쪽</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T4</t>
+          <t>C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>PC1(0.73); KI23(0.61); ST16(0.51)</t>
+          <t>HT6(0.86); LU11(0.40); LU6(0.39)</t>
         </is>
       </c>
     </row>
@@ -21829,37 +21797,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LU11</t>
+          <t>HT6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>少商</t>
+          <t>陰郄</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>손가락</t>
+          <t>손목 자쪽</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -21870,7 +21838,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LI3(0.57); SI2(0.40); HT7(0.40)</t>
+          <t>HT7(0.86); LU6(0.40); LU11(0.36)</t>
         </is>
       </c>
     </row>
@@ -21882,48 +21850,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LU1</t>
+          <t>ST16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>中府</t>
+          <t>膺窗</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>3층</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>0.242</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.226</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>흉벽 전외측</t>
+          <t>흉벽 앞</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C3,C4,C5,C6,C7,C8,T1</t>
+          <t>C5,C6,C7,C8,T1,T3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>KI27(0.38); SP18(0.34); LU3(0.33)</t>
+          <t>KI24(0.72); ST18(0.61); SP18(0.51)</t>
         </is>
       </c>
     </row>
@@ -21935,12 +21903,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PC1</t>
+          <t>SP18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天池</t>
+          <t>天谿</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21950,17 +21918,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.267</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21976,7 +21944,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SP18(0.73); KI23(0.59); ST16(0.49)</t>
+          <t>PC1(0.73); KI23(0.61); ST16(0.51)</t>
         </is>
       </c>
     </row>
@@ -21988,48 +21956,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ST18</t>
+          <t>LU11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>乳根</t>
+          <t>少商</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>흉벽 앞</t>
+          <t>손가락</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T5</t>
+          <t>C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>KI22(0.69); ST16(0.61); KI25(0.49)</t>
+          <t>LI3(0.46); LI1(0.46); SI2(0.45)</t>
         </is>
       </c>
     </row>
@@ -22041,12 +22009,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KI25</t>
+          <t>PC1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>神藏</t>
+          <t>天池</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22056,33 +22024,33 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.263</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>흉벽 앞(흉골 옆)</t>
+          <t>흉벽 전외측</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T2</t>
+          <t>C5,C6,C7,C8,T1,T4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>KI24(0.58); KI23(0.58); KI22(0.51)</t>
+          <t>SP18(0.73); KI23(0.59); ST16(0.49)</t>
         </is>
       </c>
     </row>
@@ -22094,48 +22062,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KI23</t>
+          <t>LU1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>神封</t>
+          <t>中府</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.262</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.237</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>흉벽 앞(흉골 옆)</t>
+          <t>흉벽 전외측</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T4</t>
+          <t>C3,C4,C5,C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SP18(0.61); PC1(0.59); KI25(0.58)</t>
+          <t>KI27(0.38); SP18(0.34); LU3(0.33)</t>
         </is>
       </c>
     </row>
@@ -22147,12 +22115,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KI24</t>
+          <t>ST18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>靈墟</t>
+          <t>乳根</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22167,28 +22135,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>흉벽 앞(흉골 옆)</t>
+          <t>흉벽 앞</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T3</t>
+          <t>C5,C6,C7,C8,T1,T5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ST16(0.72); KI25(0.58); KI23(0.58)</t>
+          <t>KI22(0.69); ST16(0.61); KI25(0.49)</t>
         </is>
       </c>
     </row>
@@ -22200,32 +22168,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KI22</t>
+          <t>KI25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>步廊</t>
+          <t>神藏</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.256</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.193</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22235,13 +22203,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T1,T5</t>
+          <t>C5,C6,C7,C8,T1,T2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ST18(0.69); KI25(0.51); KI24(0.51)</t>
+          <t>KI24(0.58); KI23(0.58); KI22(0.51)</t>
         </is>
       </c>
     </row>
@@ -22253,48 +22221,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LI3</t>
+          <t>KI23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>三間</t>
+          <t>神封</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.256</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>손</t>
+          <t>흉벽 앞(흉골 옆)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C6,C7,C8,T1</t>
+          <t>C5,C6,C7,C8,T1,T4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LU11(0.57); SI2(0.46); HT7(0.38)</t>
+          <t>SP18(0.61); PC1(0.59); KI25(0.58)</t>
         </is>
       </c>
     </row>
@@ -22306,32 +22274,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KI27</t>
+          <t>KI24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>俞府</t>
+          <t>靈墟</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>3층</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.256</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.226</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -22341,17 +22309,13 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C3,C4,C5,C6,C7,C8,T1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CN VII</t>
-        </is>
-      </c>
+          <t>C5,C6,C7,C8,T1,T3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ST16(0.41); ST18(0.41); KI25(0.40)</t>
+          <t>ST16(0.72); KI25(0.58); KI23(0.58)</t>
         </is>
       </c>
     </row>
@@ -22363,12 +22327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GB23</t>
+          <t>KI22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>輒筋</t>
+          <t>步廊</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22378,33 +22342,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.208</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>흉벽 외측</t>
+          <t>흉벽 앞(흉골 옆)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C5,C6,C7,C8,T4,T5</t>
+          <t>C5,C6,C7,C8,T1,T5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SP18(0.51); PC1(0.41); KI22(0.34)</t>
+          <t>ST18(0.69); KI25(0.51); KI24(0.51)</t>
         </is>
       </c>
     </row>
@@ -22416,12 +22380,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ST12</t>
+          <t>KI27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>缺盆</t>
+          <t>俞府</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22431,37 +22395,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.221</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>빗장위오목</t>
+          <t>흉벽 앞(흉골 옆)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C1,C2,C3,C4,C5,C6,C7,C8,T1</t>
+          <t>C3,C4,C5,C6,C7,C8,T1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>CN VII,CN XI,CN XII</t>
+          <t>CN VII</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ST9(0.40); KI27(0.35); LU1(0.27)</t>
+          <t>ST16(0.41); ST18(0.41); KI25(0.40)</t>
         </is>
       </c>
     </row>
@@ -22473,52 +22437,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BL17</t>
+          <t>GB23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>膈俞</t>
+          <t>輒筋</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.154</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>등(흉추 옆)</t>
+          <t>흉벽 외측</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C3,C4,C5,C6,C7,C8,T7</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>CN XI</t>
-        </is>
-      </c>
+          <t>C5,C6,C7,C8,T4,T5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>BL14(0.58); BL13(0.53); GB21(0.44)</t>
+          <t>SP18(0.51); PC1(0.41); KI22(0.34)</t>
         </is>
       </c>
     </row>
@@ -22530,12 +22490,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SI2</t>
+          <t>ST12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>前谷</t>
+          <t>缺盆</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22545,33 +22505,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>손가락</t>
+          <t>빗장위오목</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C8,T1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>C1,C2,C3,C4,C5,C6,C7,C8,T1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>CN VII,CN XI,CN XII</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LI3(0.46); LU11(0.40); HT7(0.27)</t>
+          <t>ST9(0.40); KI27(0.35); LU1(0.27)</t>
         </is>
       </c>
     </row>
@@ -22583,48 +22547,52 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LR14</t>
+          <t>BL17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>期門</t>
+          <t>膈俞</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>흉벽 앞(하부)</t>
+          <t>등(흉추 옆)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C8,T1,T6</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>C3,C4,C5,C6,C7,C8,T7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CN XI</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>ST18(0.28); ST16(0.25); KI25(0.23)</t>
+          <t>BL14(0.58); BL13(0.53); GB21(0.44)</t>
         </is>
       </c>
     </row>
@@ -22661,7 +22629,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -22708,17 +22676,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.058</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.055</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -22734,7 +22702,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SI2(0.11); LR14(0.07); ST12(0.07)</t>
+          <t>ST12(0.07); ST9(0.06); LU11(0.06)</t>
         </is>
       </c>
     </row>
@@ -22746,48 +22714,48 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CV22</t>
+          <t>LR14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>天突</t>
+          <t>期門</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>목 앞(흉골위패임)</t>
+          <t>흉벽 앞(하부)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C1,C2,C3,C4,T1</t>
+          <t>C8,T1,T6,T8,T9,T10,T11,T12,L1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CV21(0.57); ST9(0.42); ST12(0.25)</t>
+          <t>ST18(0.18); KI25(0.15); KI24(0.15)</t>
         </is>
       </c>
     </row>
@@ -22799,48 +22767,48 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CV21</t>
+          <t>CV22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>璇璣</t>
+          <t>天突</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>0.037</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>앞 정중(흉골)</t>
+          <t>목 앞(흉골위패임)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C2,C3,C4,T1</t>
+          <t>C1,C2,C3,C4,T1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>CV22(0.57); ST9(0.24); CV18(0.21)</t>
+          <t>CV21(0.57); ST9(0.42); ST12(0.25)</t>
         </is>
       </c>
     </row>
@@ -22852,17 +22820,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BL14</t>
+          <t>CV21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>厥陰俞</t>
+          <t>璇璣</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -22877,27 +22845,23 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>0.111</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>등(흉추 옆)</t>
+          <t>앞 정중(흉골)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C3,C4,C5,T4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>CN XI</t>
-        </is>
-      </c>
+          <t>C2,C3,C4,T1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>BL13(0.69); BL17(0.58); GB21(0.49)</t>
+          <t>CV22(0.57); ST9(0.24); CV18(0.21)</t>
         </is>
       </c>
     </row>
@@ -22909,32 +22873,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BL13</t>
+          <t>BL14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>肺俞</t>
+          <t>厥陰俞</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>3층</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -22944,7 +22908,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C3,C4,C5,T2,T3,T4,T5</t>
+          <t>C3,C4,C5,T4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -22954,7 +22918,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>BL14(0.69); BL17(0.53); GB21(0.42)</t>
+          <t>BL13(0.69); BL17(0.58); GB21(0.49)</t>
         </is>
       </c>
     </row>
@@ -22966,12 +22930,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GB41</t>
+          <t>BL13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>足臨泣</t>
+          <t>肺俞</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22981,33 +22945,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.023</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.073</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>발등</t>
+          <t>등(흉추 옆)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>L4,L5,S1,S2,S3,S4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>C3,C4,C5,T2,T3,T4,T5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>CN XI</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>KI4(0.30); GV14(0.01); LU8(0.01)</t>
+          <t>BL14(0.69); BL17(0.53); GB21(0.42)</t>
         </is>
       </c>
     </row>
@@ -23019,17 +22987,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KI4</t>
+          <t>GB41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>大鐘</t>
+          <t>足臨泣</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -23039,28 +23007,28 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>발목 안쪽</t>
+          <t>발등</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>L2,L3,L4,L5,S1,S2,S3,S4</t>
+          <t>L4,L5,S1,S2,S3,S4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>GB41(0.30); SI2(0.02); LI1(0.02)</t>
+          <t>KI4(0.30); GV14(0.01); LU8(0.01)</t>
         </is>
       </c>
     </row>
@@ -23072,48 +23040,48 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CV15</t>
+          <t>KI4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>鳩尾</t>
+          <t>大鐘</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1층</t>
+          <t>2층</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.009</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>앞 정중(명치)</t>
+          <t>발목 안쪽</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>T6</t>
+          <t>L2,L3,L4,L5,S1,S2,S3,S4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LR14(0.22); CV18(0.02); CV21(0.02)</t>
+          <t>GB41(0.30); SI2(0.02); LU11(0.01)</t>
         </is>
       </c>
     </row>
@@ -23125,12 +23093,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CV18</t>
+          <t>CV15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>玉堂</t>
+          <t>鳩尾</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -23150,23 +23118,23 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>앞 정중(흉골)</t>
+          <t>앞 정중(명치)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>KI24(0.26); CV21(0.21); ST16(0.16)</t>
+          <t>LR14(0.07); CV18(0.02); CV21(0.02)</t>
         </is>
       </c>
     </row>
@@ -23178,12 +23146,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ST9</t>
+          <t>CV18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>人迎</t>
+          <t>玉堂</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23203,27 +23171,23 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>목 앞</t>
+          <t>앞 정중(흉골)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C1,C2,C3,C4</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>CN VII,CN X,CN XII</t>
-        </is>
-      </c>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CV22(0.42); ST12(0.40); CV21(0.24)</t>
+          <t>KI24(0.26); CV21(0.21); ST16(0.16)</t>
         </is>
       </c>
     </row>
@@ -23235,17 +23199,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LI1</t>
+          <t>ST9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>商陽</t>
+          <t>人迎</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3층</t>
+          <t>1층</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -23260,19 +23224,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>손가락</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>목 앞</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C1,C2,C3,C4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>CN VII,CN X,CN XII</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LU11(0.25); SI2(0.22); LI3(0.19)</t>
+          <t>CV22(0.42); ST12(0.40); CV21(0.24)</t>
         </is>
       </c>
     </row>
@@ -23377,7 +23349,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="3">
@@ -23497,193 +23469,191 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A4 명치(鳩尾)</t>
+          <t>A1 수태음 본경·손목 자쪽</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CV15</t>
+          <t>HT7, LI3, LU11, LU5, LU7, LU9, SI2, HT6, LU3, LU4, LU6, LU8, LI1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>13/13</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>0/13</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.418</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A5 갈비활(期門)</t>
+          <t>A2 앞가슴벽</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LR14</t>
+          <t>KI25, KI27, PC1, SP18, KI22, KI23, KI24, ST16, ST18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>0/9</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.493</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HT7, LU5, LU7, LU9, HT6, LU3, LU4, LU6, LU8</t>
+          <t>LU1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/9</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.486</v>
-      </c>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KI25, KI27, LU1, PC1, SP18, GB23, KI22, KI23, KI24, ST16, ST18</t>
+          <t>GB23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11/11</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/11</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.425</v>
-      </c>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A3 손가락</t>
+          <t>A5 갈비활(期門)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LI3, LU11, SI2</t>
+          <t>LR14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0/3</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/3</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.478</v>
-      </c>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A6 집게손가락 끝(商陽)</t>
+          <t>D2 C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -23691,7 +23661,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LI1</t>
+          <t>GV14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -23701,7 +23671,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -23719,7 +23689,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>D1 흉골 정중(玉堂)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -23727,17 +23697,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GV14</t>
+          <t>CV18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>0/1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1/1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -23755,7 +23725,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D1 흉골 정중(玉堂)</t>
+          <t>A4 명치(鳩尾)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -23763,12 +23733,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CV18</t>
+          <t>CV15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">

--- a/04_번역원고_및_임상매트릭스/영추경맥_수태음시동병_매트릭스/영추경맥_수태음시동병_해부임상_매트릭스.xlsx
+++ b/04_번역원고_및_임상매트릭스/영추경맥_수태음시동병_매트릭스/영추경맥_수태음시동병_해부임상_매트릭스.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"A1_수태음본경_아래팔": ["Cephalic vein", "Radial artery", "Radial vein", "Brachioradialis", "Pronator quadratus", "Flexor digitorum superficialis", "Set of dorsal digital veins"], "A2_앞가슴벽": ["External intercostal muscle", "Internal intercostal muscle", "Internal thoracic vein", "Internal thoracic artery", "Transversus thoracis", "Pectoralis minor", "Lateral thoracic artery"], "B2_목앞_빗장위": ["Common carotid artery", "Internal thoracic vein", "Sternohyoid", "Omohyoid", "Sternocleidomastoid", "Platysma"], "B1_등_흉추옆": ["Transverse cervical artery", "Splenius cervicis", "Longissimus", "Rhomboid major"]}</t>
+          <t>{"A1_상지": ["Cephalic vein", "Radial artery", "Radial vein", "Brachioradialis", "Pronator quadratus", "Flexor digitorum superficialis", "Set of dorsal digital veins"], "A2a_앞가슴벽": ["External intercostal muscle", "Internal intercostal muscle", "Internal thoracic vein", "Internal thoracic artery", "Transversus thoracis", "Pectoralis minor", "Lateral thoracic artery"], "B2_목앞_빗장위": ["Common carotid artery", "Internal thoracic vein", "Sternohyoid", "Omohyoid", "Sternocleidomastoid", "Platysma"], "B1_등_흉추옆": ["Transverse cervical artery", "Splenius cervicis", "Longissimus", "Rhomboid major"]}</t>
         </is>
       </c>
     </row>
@@ -19945,9 +19945,9 @@
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>대분류(5군)</t>
+          <t>대분류(8군)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>소분류 번호(16군)</t>
+          <t>소분류(16군)</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20008,8 +20008,10 @@
           <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>3</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>B1 등 흉추 옆·어깨 위</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -20030,7 +20032,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20038,8 +20040,10 @@
           <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>B1 등 흉추 옆·어깨 위</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -20060,16 +20064,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>D 명치(鳩尾)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A4 명치(鳩尾)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>16</v>
+          <t>D 명치(鳩尾)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D 명치(鳩尾)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -20090,16 +20096,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D1 흉골 정중(玉堂)</t>
+          <t>D 흉골 정중(玉堂)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>D1 흉골 정중(玉堂)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>15</v>
+          <t>D 흉골 정중(玉堂)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>D 흉골 정중(玉堂)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -20120,7 +20128,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B2 목 앞·빗장위</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -20128,8 +20136,10 @@
           <t>B2a 흉골위패임·흉골자루</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>4</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B2a 흉골위패임·흉골자루</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -20158,8 +20168,10 @@
           <t>C 하지 원위</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C1 발등(足臨泣)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -20180,16 +20192,18 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>A1b 손목 자쪽(陰郄·神門)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -20210,16 +20224,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -20240,16 +20256,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A2b 빗장 아래(俞府)</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -20270,16 +20288,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>7</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>A1c 손가락(少商·三間·前谷·商陽)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -20300,16 +20320,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>11</v>
+          <t>A2c 앞가슴벽 바깥(中府)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>A2c 앞가슴벽 바깥(中府)</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -20330,16 +20352,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>7</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>A1c 손가락(少商·三間·前谷·商陽)</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -20360,16 +20384,18 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -20390,16 +20416,18 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -20420,16 +20448,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -20450,16 +20480,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -20480,16 +20512,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>7</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>A1c 손가락(少商·三間·前谷·商陽)</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -20510,16 +20544,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -20540,7 +20576,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B2 목 앞·빗장위</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -20548,8 +20584,10 @@
           <t>B2b 목 앞·빗장위</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>5</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B2b 목 앞·빗장위</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -20570,7 +20608,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B2 목 앞·빗장위</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20578,8 +20616,10 @@
           <t>B2b 목 앞·빗장위</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>5</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>B2b 목 앞·빗장위</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -20600,7 +20640,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B2 목 앞·빗장위</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20608,8 +20648,10 @@
           <t>B2a 흉골위패임·흉골자루</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>4</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>B2a 흉골위패임·흉골자루</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -20630,16 +20672,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>12</v>
+          <t>A2d 옆가슴(輒筋)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>A2d 옆가슴(輒筋)</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -20660,16 +20704,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>6</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>A1b 손목 자쪽(陰郄·神門)</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -20690,16 +20736,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -20720,16 +20768,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -20758,8 +20808,10 @@
           <t>C 하지 원위</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C2 발목 안쪽(大鐘)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -20780,16 +20832,18 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>D 갈비활(期門)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A5 갈비활(期門)</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>13</v>
+          <t>D 갈비활(期門)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>D 갈비활(期門)</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -20810,16 +20864,18 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -20840,16 +20896,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -20870,16 +20928,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -20900,16 +20960,18 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>8</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -20930,7 +20992,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -20938,8 +21000,10 @@
           <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>3</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>B1 등 흉추 옆·어깨 위</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -20960,7 +21024,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -20968,8 +21032,10 @@
           <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>3</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>B1 등 흉추 옆·어깨 위</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -20990,16 +21056,18 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>D C7 극돌기(大椎)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>14</v>
+          <t>D C7 극돌기(大椎)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>D C7 극돌기(大椎)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -21020,16 +21088,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -21050,16 +21120,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>7</v>
+          <t>A1 상지(수태음 본경·손목·손가락)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>A1c 손가락(少商·三間·前谷·商陽)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -21080,16 +21152,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -21110,16 +21184,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A 팔신경얼기 영역</t>
+          <t>A 팔신경얼기 영역(상지·앞가슴벽)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>9</v>
+          <t>A2 앞가슴벽(늑간·가슴근신경)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>A2a 앞가슴벽 2~5늑간</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23259,7 +23335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23275,7 +23351,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>중분류</t>
+          <t>소분류</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -23317,121 +23393,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C 하지 원위</t>
+          <t>C1 발등(足臨泣)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GB41, KI4</t>
+          <t>GB41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.301</v>
-      </c>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B1 등 흉추 옆·어깨 위</t>
+          <t>C2 발목 안쪽(大鐘)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BL13, BL17, BL14, GB21</t>
+          <t>KI4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>0/1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.525</v>
-      </c>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B2a 흉골위패임·흉골자루</t>
+          <t>B1 등 흉추 옆·어깨 위</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CV22, CV21</t>
+          <t>BL13, BL17, BL14, GB21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2/2</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.571</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B2b 목 앞·빗장위</t>
+          <t>B2a 흉골위패임·흉골자루</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -23439,17 +23511,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST12, ST9</t>
+          <t>CV22, CV21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -23459,201 +23531,207 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.399</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A1 수태음 본경·손목 자쪽</t>
+          <t>B2b 목 앞·빗장위</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HT7, LI3, LU11, LU5, LU7, LU9, SI2, HT6, LU3, LU4, LU6, LU8, LI1</t>
+          <t>ST12, ST9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0/13</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0/13</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.418</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A2 앞가슴벽</t>
+          <t>A1b 손목 자쪽(陰郄·神門)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KI25, KI27, PC1, SP18, KI22, KI23, KI24, ST16, ST18</t>
+          <t>HT7, HT6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0/9</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.493</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>A1c 손가락(少商·三間·前谷·商陽)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LU1</t>
+          <t>LI3, LU11, SI2, LI1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>0/4</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.536</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>A1a 수태음 본경 사슬(天府~太淵)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GB23</t>
+          <t>LU5, LU7, LU9, LU3, LU4, LU6, LU8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>0/7</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.584</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A5 갈비활(期門)</t>
+          <t>A2a 앞가슴벽 2~5늑간</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LR14</t>
+          <t>KI25, PC1, SP18, KI22, KI23, KI24, ST16, ST18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>0/8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>0/8</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.522</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D2 C7 극돌기(大椎)</t>
+          <t>A2b 빗장 아래(俞府)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -23661,12 +23739,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GV14</t>
+          <t>KI27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -23676,7 +23754,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -23689,7 +23767,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D1 흉골 정중(玉堂)</t>
+          <t>A2c 앞가슴벽 바깥(中府)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -23697,7 +23775,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CV18</t>
+          <t>LU1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -23707,12 +23785,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -23725,7 +23803,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A4 명치(鳩尾)</t>
+          <t>A2d 옆가슴(輒筋)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -23733,30 +23811,174 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>GB23</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D 갈비활(期門)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LR14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D C7 극돌기(大椎)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GV14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D 흉골 정중(玉堂)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CV18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D 명치(鳩尾)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>CV15</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
